--- a/data/EVALUACIONES/FUERZA TREN SUPERIOR/FUERZA_TS.xlsx
+++ b/data/EVALUACIONES/FUERZA TREN SUPERIOR/FUERZA_TS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30411"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\FUERZA TREN SUPERIOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755691EC-33C3-4437-A31E-D0E3F073D7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{755691EC-33C3-4437-A31E-D0E3F073D7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D5F98C4C-06CB-4CB5-AD15-FF16B9CED4F3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Fecha</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>Ikki_Muller_Salak</t>
-  </si>
-  <si>
-    <t>Alejandro_Garcia_Gumiel</t>
   </si>
   <si>
     <t>Rodri_Sanchez_Ramos</t>
@@ -318,16 +315,16 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color theme="4" tint="0.39997558519241921"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -344,8 +341,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4038579-32CC-4315-96AE-2AFD5D4E1DEC}" name="Tabla1" displayName="Tabla1" ref="A1:D29" totalsRowShown="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
-  <autoFilter ref="A1:D29" xr:uid="{A4038579-32CC-4315-96AE-2AFD5D4E1DEC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A4038579-32CC-4315-96AE-2AFD5D4E1DEC}" name="Tabla1" displayName="Tabla1" ref="A1:D28" totalsRowShown="0" headerRowBorderDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A1:D28" xr:uid="{A4038579-32CC-4315-96AE-2AFD5D4E1DEC}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{07CF568F-C355-412E-AF62-0FC68FE004D5}" name="Fecha"/>
     <tableColumn id="2" xr3:uid="{61A0F3E6-BA24-4229-B91D-142FB098244E}" name="Nombre"/>
@@ -653,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.5546875" bestFit="1" customWidth="1"/>
@@ -669,10 +666,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>26</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -680,7 +677,7 @@
         <v>46247</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="5">
         <v>21</v>
@@ -694,7 +691,7 @@
         <v>46247</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="5">
         <v>26</v>
@@ -708,7 +705,7 @@
         <v>46247</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="5">
         <v>23</v>
@@ -722,7 +719,7 @@
         <v>46247</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="5">
         <v>27</v>
@@ -736,7 +733,7 @@
         <v>46247</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5">
         <v>14</v>
@@ -764,7 +761,7 @@
         <v>46247</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="5">
         <v>21</v>
@@ -778,7 +775,7 @@
         <v>46247</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="5">
         <v>20</v>
@@ -792,7 +789,7 @@
         <v>46247</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="5">
         <v>27</v>
@@ -820,7 +817,7 @@
         <v>46247</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="5">
         <v>27</v>
@@ -834,7 +831,7 @@
         <v>46247</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4"/>
@@ -858,7 +855,7 @@
         <v>46247</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="5">
         <v>21</v>
@@ -872,7 +869,7 @@
         <v>46247</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="5">
         <v>21</v>
@@ -886,7 +883,7 @@
         <v>46247</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" s="5">
         <v>20</v>
@@ -900,7 +897,7 @@
         <v>46247</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" s="5">
         <v>22</v>
@@ -928,7 +925,7 @@
         <v>46247</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="5">
         <v>27</v>
@@ -938,128 +935,114 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="6">
-        <v>46247</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>8</v>
+      <c r="A21" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C21" s="5">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D21" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <v>46247</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>23</v>
+      <c r="A22" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="C22" s="5">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D22" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="6">
-        <v>46247</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>5</v>
+      <c r="A23" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="C23" s="5">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D23" s="4">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <v>46247</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>4</v>
+      <c r="A24" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C24" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>29</v>
+      </c>
+      <c r="D25" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="5">
+        <v>30</v>
+      </c>
+      <c r="D26" s="4">
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="6">
-        <v>46247</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" s="5">
-        <v>12</v>
-      </c>
-      <c r="D25" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <v>46247</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="5">
-        <v>29</v>
-      </c>
-      <c r="D26" s="4">
-        <v>7</v>
-      </c>
-    </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="6">
-        <v>46247</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>31</v>
+      <c r="A27" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C27" s="5">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D27" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <v>46247</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>25</v>
+      <c r="A28" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C28" s="5">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D28" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="6">
-        <v>46247</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="5">
-        <v>21</v>
-      </c>
-      <c r="D29" s="4">
         <v>4</v>
       </c>
     </row>
